--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-common.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-common.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="377">
   <si>
     <t>Property</t>
   </si>
@@ -585,13 +585,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -905,7 +899,7 @@
 Period</t>
   </si>
   <si>
-    <t>診断レポートの作成日時</t>
+    <t>診断レポートの対象となる検査・処置が実施された日時</t>
   </si>
   <si>
     <t>診断手順が患者に対して実行された場合、これは実施された時間である。対象が検体である場合は、検体採取時間から診断関連時刻を導き出すことができるが、検体情報が常に入手できるとは限らず、検体と診断関連時刻の正確な関係は必ずしも自明ではない。</t>
@@ -1171,6 +1165,9 @@
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
@@ -3103,13 +3100,11 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -3145,21 +3140,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3182,13 +3177,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3239,7 +3234,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3260,7 +3255,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3268,10 +3263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3300,7 +3295,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3341,19 +3336,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3374,7 +3369,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3382,10 +3377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3408,19 +3403,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3469,7 +3464,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3487,10 +3482,10 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3498,10 +3493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3524,13 +3519,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3581,7 +3576,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3602,7 +3597,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3610,10 +3605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3642,7 +3637,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -3683,19 +3678,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AF19" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3716,7 +3711,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3724,10 +3719,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3753,16 +3748,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3811,7 +3806,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3829,10 +3824,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -3840,10 +3835,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3866,16 +3861,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3925,7 +3920,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3943,10 +3938,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -3954,10 +3949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3983,14 +3978,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4039,7 +4034,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4057,10 +4052,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4068,10 +4063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4094,17 +4089,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4153,7 +4148,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4171,10 +4166,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4182,10 +4177,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4208,19 +4203,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4269,7 +4264,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4287,10 +4282,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4298,10 +4293,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4324,19 +4319,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4385,7 +4380,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4403,10 +4398,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4414,14 +4409,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4443,10 +4438,10 @@
         <v>179</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4477,7 +4472,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4495,7 +4490,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -4510,28 +4505,28 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4550,19 +4545,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -4611,7 +4606,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4626,28 +4621,28 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4666,19 +4661,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -4727,7 +4722,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4742,28 +4737,28 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4782,19 +4777,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4843,7 +4838,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4858,28 +4853,28 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4898,19 +4893,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -4959,7 +4954,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4977,25 +4972,25 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5014,19 +5009,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5075,7 +5070,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5090,28 +5085,28 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5130,19 +5125,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5191,7 +5186,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5206,24 +5201,24 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5246,19 +5241,19 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5307,7 +5302,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5325,10 +5320,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5336,14 +5331,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5362,19 +5357,19 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5423,7 +5418,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5441,10 +5436,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5452,10 +5447,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5478,16 +5473,16 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5537,7 +5532,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5558,7 +5553,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5566,14 +5561,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5592,19 +5587,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5653,7 +5648,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5671,10 +5666,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5682,10 +5677,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5708,13 +5703,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5765,7 +5760,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5786,7 +5781,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5794,10 +5789,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5826,7 +5821,7 @@
         <v>138</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>140</v>
@@ -5879,7 +5874,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5900,7 +5895,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -5908,14 +5903,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5937,10 +5932,10 @@
         <v>137</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>140</v>
@@ -5995,7 +5990,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6024,10 +6019,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6050,19 +6045,19 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6111,7 +6106,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6132,7 +6127,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6140,10 +6135,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6166,13 +6161,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6223,7 +6218,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -6244,7 +6239,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6252,14 +6247,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6278,17 +6273,17 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6337,7 +6332,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6355,10 +6350,10 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6366,10 +6361,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6395,13 +6390,13 @@
         <v>179</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6427,14 +6422,14 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>182</v>
+        <v>367</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6451,7 +6446,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6469,10 +6464,10 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6480,10 +6475,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6506,19 +6501,19 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6567,7 +6562,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6585,10 +6580,10 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
